--- a/renommage-mapping/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/renommage-mapping/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T12:29:29+00:00</t>
+    <t>2025-10-21T13:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/renommage-mapping/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/renommage-mapping/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:02:53+00:00</t>
+    <t>2025-10-21T13:05:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/renommage-mapping/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/renommage-mapping/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:05:45+00:00</t>
+    <t>2025-10-21T13:27:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/renommage-mapping/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/renommage-mapping/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:27:14+00:00</t>
+    <t>2025-10-21T14:51:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
